--- a/data_extactor/batch_10_fa/batch_0085_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0085_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی انگشتان | چالاکی دست | بینایی نزدیک | قدرت بالاتنه | قدرت ایستا | دقت کنترل | درک شفاهی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | مهارت دستی | بینایی نزدیک | قدرت تنه | قدرت ایستا | دقت کنترل | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان در حالت ایستاده | صرف زمان برای انجام حرکات تکراری | سرعت تعیین‌شده توسط سرعت تجهیزات | داخل ساختمان، با تهویه مطبوع | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض سوختگی‌های خفیف، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | سرعت تعیین‌شده توسط سرعت تجهیزات | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | پرورش‌دهندگان حیوانات | دانشمندان علوم دامی | نانواها | قصاب‌ها و برش‌دهندگان گوشت | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، رستوران | آشپزها، سفارش‌های سریع | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | کارگران کشاورزی و کارگران ساده، زراعت، گلخانه و نهالستان | کارگران کشاورزی، مزارع، دامداری‌ها و آبزی‌پروری | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | دانشمندان و متخصصان صنایع غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و لفاف‌پیچ‌های دستی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | پرورش‌دهندگان حیوانات | دانشمندان علوم دامی | نانوایان | قصابان و برش‌دهندگان گوش | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | درک مطلب خواندن | گوش دادن فعال | سخن گفتن</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | امنیت و ایمنی عمومی | تولید مواد غذایی</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مشکلات | تشخیص گفتار | دقت کنترل | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص رنگ بصری | قدرت بالاتنه | کنترل سرعت | هماهنگی چند عضو | چالاکی انگشتان | چالاکی دست | انعطاف‌پذیری بستار | بیان کتبی | بیان شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | دقت کنترل | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص رنگ بصری | قدرت تنه | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری بستار | بیان کتبی | بیان شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان در حالت ایستاده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، بدون تهویه مطبوع | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | پیامد خطا | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | نانواها | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان نوار نقاله | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان کوره، تنور، فر، خشک‌کن و دیگ پخت | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و همزن | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و لفاف‌پیچ‌های دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداساز، فیلتر، شفاف‌ساز، رسوب‌دهنده و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورهای تجهیزات کشاورزی | نانوایان | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان نوار نقاله | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | تولید مواد غذایی | تولید و فرآوری | آموزش و پرورش | زبان انگلیسی | مکانیک | امور اداری و مدیریت | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فرآوری | آموزش و پرورش | زبان انگلیسی | مکانیک | مدیریت و اداره | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | دقت کنترل | حساسیت به مشکلات | درک کتبی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تشخیص گفتار | توجه شنیداری | چالاکی دست | توجه انتخابی | سرعت ادراکی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | دقت کنترل | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تشخیص گفتار | توجه شنیداری | مهارت دستی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان در حالت ایستاده | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، با تهویه مطبوع | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های چسب‌زنی و اتصال | نانواها | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | آشپزها، رستوران | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | تکنسین‌های علوم غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، تنور، فر، خشک‌کن و دیگ پخت | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و همزن | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و لفاف‌پیچ‌های دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداساز، فیلتر، شفاف‌ساز، رسوب‌دهنده و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | نانوایان | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | آشپزها، رستوران | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | تکنسین‌های علوم غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | پایش | تفکر انتقادی | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | تولید مواد غذایی | امور اداری و مدیریت | آموزش و پرورش | مکانیک</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | مدیریت و اداره | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | درک کتبی | درک شفاهی | بینایی نزدیک | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | چالاکی دست | ثبات دست و بازو | زمان عکس‌العمل | چالاکی انگشتان</t>
+          <t>حساسیت به مسئله | درک کتبی | درک شفاهی | بینایی نزدیک | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | مهارت دستی | ثبات دست و بازو | زمان عکس‌العمل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، با تهویه مطبوع | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان در حالت ایستاده | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | پیامد خطا | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارگران | تعداد دفعات تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای ایستادن | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | پیامد خطا | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های چسب‌زنی و اتصال | نانواها | اپراتورها و متصدیان تجهیزات تمیزکاری, شستشو و اسیدشویی فلزات | آشپزها، رستوران | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، تنور، فر، خشک‌کن و دیگ پخت | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و همزن | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و لفاف‌پیچ‌های دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداساز، فیلتر، شفاف‌ساز، رسوب‌دهنده و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | نانوایان | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | آشپزها، رستوران | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی | شیمی | مکانیک | امنیت و ایمنی عمومی | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی | شیمی | مکانیک | ایمنی و امنیت عمومی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مشکلات | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>داخل ساختمان، بدون تهویه مطبوع | صرف زمان در حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد خطا | میزان اتوماسیون | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های خفیف، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بچ‌سازان مواد غذایی | نانواها | قصاب‌ها و برش‌دهندگان گوشت | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | ذبح‌کنندگان و بسته‌بندندگان گوشت | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و همزن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداساز، فیلتر، شفاف‌ساز، رسوب‌دهنده و تقطیر | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌بردارها و توزین‌کنندگان | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | کمک‌کارگران--کارگران تولیدی | کارگران تولیدی، سایر | سرپرستان خط اول کارگران تولیدی و عملیاتی | تکنسین‌های علوم غذایی | دانشمندان و متخصصان صنایع غذایی | مکانیک‌های ماشین‌آلات صنعتی | بسته‌بندها و لفاف‌پیچ‌های دستی</t>
+          <t>بچ‌سازان مواد غذایی | نانوایان | قصابان و برش‌دهندگان گوش | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | ذبح‌کنندگان و بسته‌بندندگان گوشت | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | کمک‌کاران--کارگران تولید | کارگران تولید، سایر موارد | سرپرستان رده اول کارگران تولید و بهره‌برداری | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | مکانیک‌های ماشین‌آلات صنعتی | بسته‌بندهای دستی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | پایش | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | چالاکی دست | حساسیت به مشکلات | بینایی نزدیک | کنترل سرعت | قدرت بالاتنه | قدرت ایستا | ثبات دست و بازو | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | سرعت ادراکی | استدلال قیاسی | درک شفاهی | چالاکی انگشتان | توجه انتخابی | تجسم فضایی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تشخیص رنگ بصری | بینایی دور | استقامت</t>
+          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی | حساسیت به مسئله | بینایی نزدیک | کنترل نرخ | قدرت تنه | قدرت ایستا | ثبات دست و بازو | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | سرعت ادراکی | استدلال قیاسی | درک شفاهی | مهارت انگشتان | توجه انتخابی | تجسم | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تشخیص رنگ بصری | بینایی دور | استقامت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعداد دفعات تصمیم‌گیری | صرف زمان در حالت ایستاده | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های خفیف، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | داخل ساختمان، بدون تهویه مطبوع | برخورد با افراد ناراحت، عصبانی یا بی‌ادب</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش و چرخ‌کاری، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تیزکنندگان و پرداخت‌کنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>پایش | درک مطلب خواندن | گوش دادن فعال</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | چالاکی دست | توجه انتخابی | تجسم فضایی | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | توجه شنیداری | کنترل سرعت | هماهنگی چند عضو | چالاکی انگشتان</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | مهارت دستی | توجه انتخابی | تجسم | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | توجه شنیداری | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان در حالت ایستاده | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | درون یک وسیله نقلیه روباز یا کاربری تجهیزات | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض سوختگی‌های خفیف، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | تعداد دفعات تصمیم‌گیری | داخل ساختمان، بدون تهویه مطبوع | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | در یک وسیله نقلیه روباز یا کار با تجهیزات | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش و چرخ‌کاری، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری، ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تیزکنندگان و پرداخت‌کنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب، به جز اره‌کاری</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب خواندن</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | دقت کنترل | زمان عکس‌العمل | بینایی نزدیک | کنترل سرعت | چالاکی دست | هماهنگی چند عضو | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | چالاکی انگشتان | جهت‌یابی پاسخ | قدرت ایستا | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | بینایی دور | قدرت بالاتنه | توجه انتخابی | استدلال استقرایی | درک کتبی | درک شفاهی | تجسم فضایی | انعطاف‌پذیری بستار | درک عمق | استقامت</t>
+          <t>حساسیت به مسئله | دقت کنترل | زمان عکس‌العمل | بینایی نزدیک | کنترل نرخ | مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | مهارت انگشتان | جهت‌گیری پاسخ | قدرت ایستا | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | بینایی دور | قدرت تنه | توجه انتخابی | استدلال استقرایی | درک کتبی | درک شفاهی | تجسم | انعطاف‌پذیری بستار | درک عمق | استقامت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فشار زمانی | صرف زمان در حالت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض آلاینده‌ها | تعداد دفعات تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای راه رفتن یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های خفیف، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | پیامدهای کاری و نتایج سایر کارگران | داخل ساختمان، بدون تهویه مطبوع | آزادی در تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فشار زمانی | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای راه رفتن یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش و چرخ‌کاری، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره، فلز و پلاستیک | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تیزکنندگان و پرداخت‌کنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | پایش | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | ترتیب‌دهی اطلاعات | چالاکی دست | زمان عکس‌العمل | توجه انتخابی | درک کتبی | درک شفاهی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | حساسیت به مشکلات | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک عمق | بینایی دور | قدرت بالاتنه | قدرت ایستا | کنترل سرعت | هماهنگی چند عضو | چالاکی انگشتان</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | ترتیب‌دهی اطلاعات | مهارت دستی | زمان عکس‌العمل | توجه انتخابی | درک کتبی | درک شفاهی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک عمق | بینایی دور | قدرت تنه | قدرت ایستا | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض سوختگی‌های خفیف، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | داخل ساختمان، بدون تهویه مطبوع | صرف زمان در حالت ایستاده | پیامد خطا</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | پیامد خطا</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش و چرخ‌کاری، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کاری، چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تیزکنندگان و پرداخت‌کنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | پایش | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | امور اداری و مدیریت</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | توجه انتخابی | چالاکی دست | چالاکی انگشتان | زمان عکس‌العمل | کنترل سرعت | تجسم فضایی | درک کتبی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | بینایی دور</t>
+          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | مهارت دستی | مهارت انگشتان | زمان عکس‌العمل | کنترل نرخ | تجسم | درک کتبی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | بینایی دور</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان در حالت ایستاده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سرعت تعیین‌شده توسط سرعت تجهیزات | داخل ساختمان، با تهویه مطبوع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعداد دفعات تصمیم‌گیری | پیامد خطا | سلامت و ایمنی سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سرعت تعیین‌شده توسط سرعت تجهیزات | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | پیامد خطا | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | حفاران زمین، به جز نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش و چرخ‌کاری، فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کاری، چوب | تیزکنندگان و پرداخت‌کنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | حفاران زمین، به جز نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0085_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0085_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | تولید و فراوری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دید نزدیک | استحکام تنه | قدرت ایستا | دقت کنترل | درک شفاهی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | مهارت دستی | بینایی نزدیک | قدرت تنه | قدرت ایستا | دقت کنترل | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات و ماشین‌آلات کشاورزی | پرورش‌دهندگان دام و طیور | متخصصان علوم دامی | نانوایان و شیرینی‌پزان | قصابان و قطعه‌کاران گوشت | آشپزهای سازمانی و غذاخوری‌ها | آشپزهای رستوران | آشپزهای غذاهای فوری | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | کارگران زراعت، باغبانی و گلخانه | کارگران مزارع پرورش دام، طیور و آبزیان | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | کارشناسان و متخصصان صنایع غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورهای ماشین‌های بسته‌بندی و پرکن | کارگران دستی بسته‌بندی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | متخصصان علوم دامی | نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران | آشپزان غذاهای فوری | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft Excel | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار ایمیل</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فراوری | زبان انگلیسی | ایمنی و امنیت عمومی | تولید مواد غذایی</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | تشخیص گفتار | دقت کنترل | ثبات دست و بازو | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | درک شفاهی | تشخیص تمایز رنگ‌ها | استحکام تنه | کنترل نرخ فرایند | هماهنگی چند اندام | چابکی انگشتان | چابکی دستی | انعطاف‌پذیری تطابق شکل | بیان کتبی | بیان شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | دقت کنترل | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص رنگ بصری | قدرت تنه | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری بستار | بیان کتبی | بیان شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات و ماشین‌آلات کشاورزی | نانوایان و شیرینی‌پزان | اپراتورهای تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | اپراتورهای نوار نقاله و سیستم‌های انتقال | اپراتورهای تجهیزات سرمایشی و انجماد مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، آسیاب و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | تنظیم‌کنندگان و اپراتورهای کوره‌های عملیات حرارتی فلزات و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | اپراتورهای کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | اپراتورهای ماشین‌های بسته‌بندی و پرکن | کارگران دستی بسته‌بندی | تنظیم‌کنندگان و اپراتورهای ماشین‌های جداسازی، فیلتراسیون و تقطیر | اپراتورهای تجهیزات سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | نانوایان و شیرینی‌پزان | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان نوار نقاله | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,22 +617,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Office | نرم‌افزار Plex Manufacturing Cloud | نرم‌افزار تخصصی Edible Software</t>
+          <t>Microsoft Office | نرم‌افزار Microsoft Office | نرم‌افزار تخصصی Edible Software</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فراوری | آموزش و تعلیم | زبان انگلیسی | مکانیک | مدیریت و امور اداری | ریاضیات | رایانه و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فرآوری | آموزش و پرورش | زبان انگلیسی | مکانیک | مدیریت و اداره | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | دید نزدیک | درک شفاهی | دقت کنترل | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | تشخیص گفتار | توجه شنیداری | چابکی دستی | توجه انتخابی | سرعت ادراک</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | دقت کنترل | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تشخیص گفتار | توجه شنیداری | مهارت دستی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های اتصال با چسب | نانوایان و شیرینی‌پزان | اپراتورهای تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | آشپزهای رستوران | اپراتورهای تجهیزات سرمایشی و انجماد مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، آسیاب و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | اپراتورهای ماشین‌آلات پخت مواد غذایی | تکنسین‌های علوم و صنایع غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | اپراتورهای ماشین‌های بسته‌بندی و پرکن | کارگران دستی بسته‌بندی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های جداسازی، فیلتراسیون و تقطیر | اپراتورهای تجهیزات سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | نانوایان و شیرینی‌پزان | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | آشپزان رستوران | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورهای ماشین‌آلات پخت مواد غذایی | تکنسین‌های علوم و صنایع غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فراوری | تولید مواد غذایی | مدیریت و امور اداری | آموزش و تعلیم | مکانیک</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | مدیریت و اداره | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | درک شفاهی | دید نزدیک | دقت کنترل | توجه انتخابی | مرتب‌سازی اطلاعات | چابکی دستی | ثبات دست و بازو | زمان واکنش | چابکی انگشتان</t>
+          <t>حساسیت به مسئله | درک کتبی | درک شفاهی | بینایی نزدیک | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | مهارت دستی | ثبات دست و بازو | زمان عکس‌العمل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های اتصال با چسب | نانوایان و شیرینی‌پزان | اپراتورهای تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | آشپزهای رستوران | اپراتورهای تجهیزات سرمایشی و انجماد مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، آسیاب و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | تنظیم‌کنندگان و اپراتورهای کوره‌های عملیات حرارتی فلزات و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | اپراتورهای کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | اپراتورهای ماشین‌های بسته‌بندی و پرکن | کارگران دستی بسته‌بندی | تنظیم‌کنندگان و اپراتورهای ماشین‌های جداسازی، فیلتراسیون و تقطیر | اپراتورهای تجهیزات سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | نانوایان و شیرینی‌پزان | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | آشپزان رستوران | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | تولید و فراوری | زبان انگلیسی | شیمی | مکانیک | ایمنی و امنیت عمومی | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی | شیمی | مکانیک | ایمنی و امنیت عمومی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چند اندام | دقت کنترل | قدرت ایستا | استحکام تنه | استقامت | دید نزدیک | دید دور | ادراک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری دامنه‌ای | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | نانوایان و شیرینی‌پزان | قصابان و قطعه‌کاران گوشت | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | قصابان و بسته‌بندی‌کنندگان گوشت | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورهای ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های جداسازی، فیلتراسیون و تقطیر | اپراتورهای تجهیزات سرمایشی و انجماد مواد | بازرسان، آزمون‌گران، سورت‌کنندگان، نمونه‌برداران و توزین‌گران | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | کارگران کمکی خطوط تولید | سایر کارگران تولیدی و صنعتی | سرپرستان رده‌اول کارگران تولیدی و عملیاتی | تکنسین‌های علوم و صنایع غذایی | کارشناسان و متخصصان صنایع غذایی | مکانیک‌های ماشین‌آلات صنعتی | کارگران دستی بسته‌بندی</t>
+          <t>تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | قصابان و بسته‌بندی‌کنندگان گوشت | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کمک‌کارگران خطوط تولید | سایر کارگران خطوط تولید | سرپرستان رده اول کارگران تولید و عملیات | تکنسین‌های علوم و صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | مکانیک‌های ماشین‌آلات صنعتی | کارگران بسته‌بندی دستی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فراوری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند اندام | زمان واکنش | چابکی دستی | حساسیت به مسئله | دید نزدیک | کنترل نرخ فرایند | استحکام تنه | قدرت ایستا | ثبات دست و بازو | انعطاف‌پذیری تطابق شکل | مرتب‌سازی اطلاعات | سرعت ادراک | استدلال قیاسی | درک شفاهی | چابکی انگشتان | توجه انتخابی | تجسم فضایی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تشخیص تمایز رنگ‌ها | دید دور | استقامت</t>
+          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی | حساسیت به مسئله | بینایی نزدیک | کنترل نرخ | قدرت تنه | قدرت ایستا | ثبات دست و بازو | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | سرعت ادراکی | استدلال قیاسی | درک شفاهی | مهارت انگشتان | توجه انتخابی | تجسم | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تشخیص رنگ بصری | بینایی دور | استقامت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های اتصال با چسب | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سمباده‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب (قالب‌سازان) | تنظیم‌کنندگان و اپراتورهای ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل دستگاه | نرم‌افزار ردیابی موجودی انبار | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار ردیابی موجودی انبار | نرم‌افزار ایمیل</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فراوری | ریاضیات | آموزش و تعلیم | مکانیک | مهندسی و فناوری | طراحی</t>
+          <t>تولید و فرآوری | ریاضیات | آموزش و پرورش | مکانیک | مهندسی و فناوری | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | ثبات دست و بازو | دقت کنترل | زمان واکنش | چابکی دستی | توجه انتخابی | تجسم فضایی | سرعت ادراک | استدلال استقرایی | استدلال قیاسی | توجه شنیداری | کنترل نرخ فرایند | هماهنگی چند اندام | چابکی انگشتان</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | مهارت دستی | توجه انتخابی | تجسم | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | توجه شنیداری | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سمباده‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب (قالب‌سازان) | تنظیم‌کنندگان و اپراتورهای ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کشی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار مرورگر وب | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | زبان انگلیسی | آموزش و تعلیم</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | زمان واکنش | دید نزدیک | کنترل نرخ فرایند | چابکی دستی | هماهنگی چند اندام | ثبات دست و بازو | استدلال قیاسی | مرتب‌سازی اطلاعات | سرعت ادراک | چابکی انگشتان | جهت‌گیری پاسخ | قدرت ایستا | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | دید دور | استحکام تنه | توجه انتخابی | استدلال استقرایی | درک کتبی | درک شفاهی | تجسم فضایی | انعطاف‌پذیری تطابق شکل | ادراک عمق | استقامت</t>
+          <t>حساسیت به مسئله | دقت کنترل | زمان عکس‌العمل | بینایی نزدیک | کنترل نرخ | مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | مهارت انگشتان | جهت‌گیری پاسخ | قدرت ایستا | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | بینایی دور | قدرت تنه | توجه انتخابی | استدلال استقرایی | درک کتبی | درک شفاهی | تجسم | انعطاف‌پذیری بستار | درک عمق | استقامت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های اتصال با چسب | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، آسیاب و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش منسوجات | سنگ‌زن‌ها، سمباده‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>تولید و فراوری</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | دید نزدیک | مرتب‌سازی اطلاعات | چابکی دستی | زمان واکنش | توجه انتخابی | درک کتبی | درک شفاهی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری تطابق شکل | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | تشخیص گفتار | ادراک عمق | دید دور | استحکام تنه | قدرت ایستا | کنترل نرخ فرایند | هماهنگی چند اندام | چابکی انگشتان</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | ترتیب‌دهی اطلاعات | مهارت دستی | زمان عکس‌العمل | توجه انتخابی | درک کتبی | درک شفاهی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک عمق | بینایی دور | قدرت تنه | قدرت ایستا | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های اتصال با چسب | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش منسوجات | سنگ‌زن‌ها، سمباده‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب (قالب‌سازان) | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل عددی رایانه‌ای CNC | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار انبارداری خودکار</t>
+          <t>نرم‌افزار خودکار موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Office | نرم‌افزار SAP | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فراوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و تعلیم | طراحی | مدیریت و امور اداری</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | ثبات دست و بازو | حساسیت به مسئله | مرتب‌سازی اطلاعات | توجه انتخابی | چابکی دستی | چابکی انگشتان | زمان واکنش | کنترل نرخ فرایند | تجسم فضایی | درک کتبی | درک شفاهی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | دید دور</t>
+          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | مهارت دستی | مهارت انگشتان | زمان عکس‌العمل | کنترل نرخ | تجسم | درک کتبی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بیان شفاهی | بینایی دور</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | حفاران زمین، به‌جز نفت و گاز | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | خط‌کشان و نشانه‌گذاران فلز و پلاستیک | ماشین‌کاران صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب | سنگ‌زن‌ها، سمباده‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب (قالب‌سازان) | تنظیم‌کنندگان و اپراتورهای ماشین‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کشی</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | حفاران زمین، به‌جز نفت و گاز | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
